--- a/results/Int Task Remove ACC 0.3/Rando_5_permute.xlsx
+++ b/results/Int Task Remove ACC 0.3/Rando_5_permute.xlsx
@@ -440,707 +440,707 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7885166057046691</v>
+        <v>0.7943498531760342</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7734886147030035</v>
+        <v>0.8016878316418525</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7786768241375166</v>
+        <v>0.8074416567925403</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.760962426802672</v>
+        <v>0.8072881785242045</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7638484622121477</v>
+        <v>0.8051545086119554</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7816862861264232</v>
+        <v>0.8084247763295727</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7909121546202325</v>
+        <v>0.8087167070217918</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7589511101952502</v>
+        <v>0.8087167070217918</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7589511101952502</v>
+        <v>0.804664022118043</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7530867377603764</v>
+        <v>0.804664022118043</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7586903044665396</v>
+        <v>0.8043720914258239</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7680546253842324</v>
+        <v>0.79632789827074</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7770808648017447</v>
+        <v>0.7972487678807549</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7951633953256745</v>
+        <v>0.7969267854996308</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6920560506929061</v>
+        <v>0.798737399756152</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6672956055844623</v>
+        <v>0.8009633712843234</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6676487129290951</v>
+        <v>0.7723165988357117</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6569030875963801</v>
+        <v>0.7740359847509144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6669886490477908</v>
+        <v>0.7735293991379459</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6667428691635326</v>
+        <v>0.7526509882712551</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7149447048924149</v>
+        <v>0.7582695808218708</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7385084488176807</v>
+        <v>0.7631057561863548</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7425611337214294</v>
+        <v>0.771318453454227</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7391685126989851</v>
+        <v>0.7589146188587227</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7242167241941855</v>
+        <v>0.7568571514433398</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7410413768825237</v>
+        <v>0.7568571514433398</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7410413768825237</v>
+        <v>0.7238056600209504</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.743067719334398</v>
+        <v>0.6972474799512304</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7692255679769203</v>
+        <v>0.7131394570089125</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7786049147390655</v>
+        <v>0.7345394793330242</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7791115003520341</v>
+        <v>0.7345394793330242</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7061019954321432</v>
+        <v>0.7277370648944756</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6814478045094705</v>
+        <v>0.719339764394759</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6882942232067728</v>
+        <v>0.7207210688097814</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.658451822849587</v>
+        <v>0.7153482561434239</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6557815156354644</v>
+        <v>0.7593943726065976</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6567946868614016</v>
+        <v>0.7593943726065976</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.633998334277815</v>
+        <v>0.599927231981866</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6331847921281747</v>
+        <v>0.5879065564198993</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6345660965431972</v>
+        <v>0.582656097058369</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5847833273229955</v>
+        <v>0.5649717514124294</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5687722167842976</v>
+        <v>0.5982743890920955</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5746516150636237</v>
+        <v>0.6166198718939433</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.573131858224718</v>
+        <v>0.6231893857434787</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5473721944601858</v>
+        <v>0.6205029794103</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.563229826730548</v>
+        <v>0.614024693902083</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5554625384232308</v>
+        <v>0.566190991362286</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5508109662905912</v>
+        <v>0.5632577318702454</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5497977950646541</v>
+        <v>0.5793922689883743</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5591309910188381</v>
+        <v>0.6254132107224426</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5501659282537393</v>
+        <v>0.6580643707176344</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5628155427335015</v>
+        <v>0.7293845414112273</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5485377706798551</v>
+        <v>0.7231659883571171</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5388503941064345</v>
+        <v>0.706587115553037</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5310509075610049</v>
+        <v>0.7164290436693971</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5397369189291296</v>
+        <v>0.6687359401026909</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.540197353734137</v>
+        <v>0.6676744715195851</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5690877595177992</v>
+        <v>0.6726630518778012</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4916263115415658</v>
+        <v>0.6516590678824721</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4916263115415658</v>
+        <v>0.6323744698023457</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4898457489739495</v>
+        <v>0.6140171809798567</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6138025260591073</v>
+        <v>0.6163783851081002</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6152943777583157</v>
+        <v>0.6222245118747103</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5408101935328765</v>
+        <v>0.6014866999811104</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5362809747050641</v>
+        <v>0.5714156921333264</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.516893342262978</v>
+        <v>0.5685468291175106</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.516893342262978</v>
+        <v>0.5561129428331015</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.516893342262978</v>
+        <v>0.5573718939432968</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5333960125701922</v>
+        <v>0.5500027905139697</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5091110281112085</v>
+        <v>0.5446160252777634</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5392539453574434</v>
+        <v>0.5398571256847492</v>
       </c>
     </row>
     <row r="73">
@@ -1150,177 +1150,177 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.548164271117751</v>
+        <v>0.5679962392457885</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5230163738773548</v>
+        <v>0.5651864063331788</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5403143406659454</v>
+        <v>0.5452170590558618</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5344810931945804</v>
+        <v>0.5873355743307059</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5179955952810262</v>
+        <v>0.5952413150619065</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5293830388267821</v>
+        <v>0.5952413150619065</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5085218003537513</v>
+        <v>0.5746580547112462</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5198180155581886</v>
+        <v>0.5474237116411657</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5108239743787887</v>
+        <v>0.5493888774406265</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5365525131798121</v>
+        <v>0.5407146720931431</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4943846272731957</v>
+        <v>0.5301933611526111</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5002951505160305</v>
+        <v>0.5223477237992203</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4999420431713977</v>
+        <v>0.4789112273109749</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5046215204437347</v>
+        <v>0.4949942472481239</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5067551903559837</v>
+        <v>0.4815010389298164</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5060489756667181</v>
+        <v>0.4799201054384971</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5049284769804063</v>
+        <v>0.5005269778304398</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.505035804440781</v>
+        <v>0.5005269778304398</v>
       </c>
     </row>
   </sheetData>
